--- a/output/planowanie/planowanie_CZNI_2025_2026-03-30.xlsx
+++ b/output/planowanie/planowanie_CZNI_2025_2026-03-30.xlsx
@@ -228,8 +228,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="T_Harmonogram_6" displayName="T_Harmonogram_6" ref="A1:H181" headerRowCount="1">
-  <autoFilter ref="A1:H181"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="T_Harmonogram_6" displayName="T_Harmonogram_6" ref="A1:H14" headerRowCount="1">
+  <autoFilter ref="A1:H14"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Data"/>
     <tableColumn id="2" name="CZNI_Kod"/>
@@ -21946,13 +21946,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H181"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -22007,27 +22007,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CZNI39690</t>
+          <t>CZNI42843</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>K 9 kolor mix</t>
+          <t>Serce solar podstawka SR</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1200</v>
+        <v>24</v>
       </c>
       <c r="E2" t="n">
         <v>24</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>45758</v>
+        <v>45820</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -22037,27 +22037,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CZNI39690</t>
+          <t>CZNI42843</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>K 9 kolor mix</t>
+          <t>Serce solar podstawka SR</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2000</v>
+        <v>40</v>
       </c>
       <c r="E3" t="n">
         <v>40</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>45758</v>
+        <v>45820</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -22067,5339 +22067,329 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CZNI39690</t>
+          <t>CZNI42843</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>K 9 kolor mix</t>
+          <t>Serce solar podstawka SR</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2400</v>
+        <v>25</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>45758</v>
+        <v>45820</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CZNI39690</t>
+          <t>CZNI42850</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>K 9 kolor mix</t>
+          <t>Serce solar podstawka ZŁ</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2800</v>
+        <v>49</v>
       </c>
       <c r="E5" t="n">
-        <v>56</v>
+        <v>1.23</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>45758</v>
+        <v>45820</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46149</v>
+        <v>46147</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CZNI39690</t>
+          <t>CZNI19456</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>K 9 kolor mix</t>
+          <t>Z 364 SR</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3200</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>0.14</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>45758</v>
+        <v>45820</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46150</v>
+        <v>46147</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CZNI39690</t>
+          <t>CZNI14475</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>K 9 kolor mix</t>
+          <t>Z 364 Zł</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3305</v>
+        <v>318</v>
       </c>
       <c r="E7" t="n">
-        <v>66.09999999999999</v>
+        <v>6.36</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>45758</v>
+        <v>45820</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46150</v>
+        <v>46147</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CZNI39096</t>
+          <t>CZNI27461</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kwadrat P 45 krzyż mix</t>
+          <t>Znicz szklany Z 503 LED sr Kerti</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>324.5</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>5.9</v>
+        <v>0.23</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>45758</v>
+        <v>45859</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46151</v>
+        <v>46147</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CZNI39096</t>
+          <t>CZNI27478</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kwadrat P 45 krzyż mix</t>
+          <t>Znicz szklany Z 503 LED zł Kerti</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>440</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>0.13</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>45758</v>
+        <v>45859</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46154</v>
+        <v>46147</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CZNI39096</t>
+          <t>CZNI25610</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kwadrat P 45 krzyż mix</t>
+          <t>Znicz szklany L 925 Anioł sr Kerti</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1760</v>
+        <v>440</v>
       </c>
       <c r="E10" t="n">
-        <v>32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>45758</v>
+        <v>45859</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46155</v>
+        <v>46147</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CZNI39096</t>
+          <t>CZNI28000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kwadrat P 45 krzyż mix</t>
+          <t>Znicz Szklany Z 436 Kalie duże sr Kerti</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2200</v>
+        <v>96</v>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>1.6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>45758</v>
+        <v>45859</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46156</v>
+        <v>46147</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CZNI39096</t>
+          <t>CZNI28376</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kwadrat P 45 krzyż mix</t>
+          <t>Znicz szklany Z 12 Róża zł Kerti</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3080</v>
+        <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>56</v>
+        <v>1.54</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>45758</v>
+        <v>45859</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46157</v>
+        <v>46147</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CZNI39096</t>
+          <t>CZNI27058</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kwadrat P 45 krzyż mix</t>
+          <t>Znicz szklany P 45 Krzyż róża zł Kerti</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2200</v>
+        <v>148.49</v>
       </c>
       <c r="E13" t="n">
-        <v>40</v>
+        <v>2.97</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>45758</v>
+        <v>45859</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46158</v>
+        <v>46148</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CZNI39096</t>
+          <t>CZNI27058</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kwadrat P 45 krzyż mix</t>
+          <t>Znicz szklany P 45 Krzyż róża zł Kerti</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1760</v>
+        <v>4.51</v>
       </c>
       <c r="E14" t="n">
-        <v>32</v>
+        <v>0.09</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>45758</v>
+        <v>45859</v>
       </c>
       <c r="H14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CZNI39096</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Kwadrat P 45 krzyż mix</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CZNI39843</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>KWK 19 róża mix</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1014.14</v>
-      </c>
-      <c r="E16" t="n">
-        <v>22.54</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>CZNI39843</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>KWK 19 róża mix</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E17" t="n">
-        <v>24</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>CZNI39843</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>KWK 19 róża mix</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E18" t="n">
-        <v>24</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>46163</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CZNI39843</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>KWK 19 róża mix</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E19" t="n">
-        <v>24</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>46164</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>CZNI39843</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>KWK 19 róża mix</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E20" t="n">
-        <v>24</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>46165</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>CZNI39843</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>KWK 19 róża mix</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E21" t="n">
-        <v>24</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46167</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CZNI39843</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>KWK 19 róża mix</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E22" t="n">
-        <v>24</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>46168</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>CZNI39843</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>KWK 19 róża mix</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E23" t="n">
-        <v>24</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>46169</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CZNI39843</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>KWK 19 róża mix</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E24" t="n">
-        <v>24</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>46170</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CZNI39843</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>KWK 19 róża mix</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>513.86</v>
-      </c>
-      <c r="E25" t="n">
-        <v>11.42</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>46170</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>CZNI40283</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Serce 1325 solar mix</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>629.04</v>
-      </c>
-      <c r="E26" t="n">
-        <v>12.58</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>46171</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>CZNI40283</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Serce 1325 solar mix</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E27" t="n">
-        <v>24</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>46172</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>CZNI40283</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Serce 1325 solar mix</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E28" t="n">
-        <v>24</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>CZNI40283</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Serce 1325 solar mix</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E29" t="n">
-        <v>24</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46175</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>CZNI40283</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Serce 1325 solar mix</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E30" t="n">
-        <v>24</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>46176</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>CZNI40283</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Serce 1325 solar mix</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>685.96</v>
-      </c>
-      <c r="E31" t="n">
-        <v>13.72</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>46176</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>CZNI40115</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>565.4400000000001</v>
-      </c>
-      <c r="E32" t="n">
-        <v>10.28</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>46177</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>CZNI40115</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E33" t="n">
-        <v>24</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>46178</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>CZNI40115</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E34" t="n">
-        <v>24</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>46179</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>CZNI40115</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E35" t="n">
-        <v>24</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>46181</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>CZNI40115</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E36" t="n">
-        <v>24</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>46182</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>CZNI40115</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E37" t="n">
-        <v>24</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>46183</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>CZNI40115</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E38" t="n">
-        <v>24</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>46184</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>CZNI40115</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E39" t="n">
-        <v>24</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>46185</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>CZNI40115</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>930.5599999999999</v>
-      </c>
-      <c r="E40" t="n">
-        <v>16.92</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>46185</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>CZNI39539</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Z 418 piórko mix</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>460.25</v>
-      </c>
-      <c r="E41" t="n">
-        <v>7.08</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>46186</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>CZNI39539</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Z 418 piórko mix</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>1560</v>
-      </c>
-      <c r="E42" t="n">
-        <v>24</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>46188</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>CZNI39539</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Z 418 piórko mix</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>1560</v>
-      </c>
-      <c r="E43" t="n">
-        <v>24</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>46189</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>CZNI39539</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Z 418 piórko mix</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>1560</v>
-      </c>
-      <c r="E44" t="n">
-        <v>24</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>46190</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>CZNI39539</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Z 418 piórko mix</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>1560</v>
-      </c>
-      <c r="E45" t="n">
-        <v>24</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>46191</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>CZNI39539</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Z 418 piórko mix</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>1560</v>
-      </c>
-      <c r="E46" t="n">
-        <v>24</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>46192</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>CZNI39539</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Z 418 piórko mix</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>1560</v>
-      </c>
-      <c r="E47" t="n">
-        <v>24</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>46193</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>CZNI39539</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Z 418 piórko mix</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>1560</v>
-      </c>
-      <c r="E48" t="n">
-        <v>24</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>46195</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>CZNI39539</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Z 418 piórko mix</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>1560</v>
-      </c>
-      <c r="E49" t="n">
-        <v>24</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>46196</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>CZNI39539</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Z 418 piórko mix</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>1560</v>
-      </c>
-      <c r="E50" t="n">
-        <v>24</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>46197</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>CZNI39539</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Z 418 piórko mix</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>1560</v>
-      </c>
-      <c r="E51" t="n">
-        <v>24</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>46198</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>CZNI39539</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Z 418 piórko mix</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>1560</v>
-      </c>
-      <c r="E52" t="n">
-        <v>24</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>46199</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>CZNI39539</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Z 418 piórko mix</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>1560</v>
-      </c>
-      <c r="E53" t="n">
-        <v>24</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>46200</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>CZNI39539</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Z 418 piórko mix</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>607.75</v>
-      </c>
-      <c r="E54" t="n">
-        <v>9.35</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>46200</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>CZNI39508</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>ZKW 9 M2 mix</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>659.25</v>
-      </c>
-      <c r="E55" t="n">
-        <v>14.65</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>46202</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>CZNI39508</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>ZKW 9 M2 mix</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E56" t="n">
-        <v>24</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>46203</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>CZNI39508</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>ZKW 9 M2 mix</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E57" t="n">
-        <v>24</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>CZNI39508</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>ZKW 9 M2 mix</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E58" t="n">
-        <v>24</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>46205</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>CZNI39508</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>ZKW 9 M2 mix</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E59" t="n">
-        <v>24</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>46206</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>CZNI39508</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>ZKW 9 M2 mix</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E60" t="n">
-        <v>24</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>46207</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>CZNI39508</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>ZKW 9 M2 mix</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E61" t="n">
-        <v>24</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>46209</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>CZNI39508</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>ZKW 9 M2 mix</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E62" t="n">
-        <v>24</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>46210</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>CZNI39508</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>ZKW 9 M2 mix</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E63" t="n">
-        <v>24</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>46211</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>CZNI39508</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>ZKW 9 M2 mix</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E64" t="n">
-        <v>24</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>46212</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>CZNI39508</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>ZKW 9 M2 mix</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E65" t="n">
-        <v>24</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>46213</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>CZNI39508</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>ZKW 9 M2 mix</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E66" t="n">
-        <v>24</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>46214</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>CZNI39508</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>ZKW 9 M2 mix</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E67" t="n">
-        <v>24</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
-        <v>46216</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>CZNI39508</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>ZKW 9 M2 mix</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E68" t="n">
-        <v>24</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
-        <v>46217</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>CZNI39508</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>ZKW 9 M2 mix</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E69" t="n">
-        <v>24</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
-        <v>46218</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>CZNI39508</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>ZKW 9 M2 mix</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E70" t="n">
-        <v>24</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
-        <v>46219</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>CZNI39508</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>ZKW 9 M2 mix</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>224.75</v>
-      </c>
-      <c r="E71" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
-        <v>46219</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>1140.34</v>
-      </c>
-      <c r="E72" t="n">
-        <v>19.01</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
-        <v>46220</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E73" t="n">
-        <v>24</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
-        <v>46221</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E74" t="n">
-        <v>24</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E75" t="n">
-        <v>24</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E76" t="n">
-        <v>24</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
-        <v>46225</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E77" t="n">
-        <v>24</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
-        <v>46226</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E78" t="n">
-        <v>24</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E79" t="n">
-        <v>24</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>46228</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E80" t="n">
-        <v>24</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>46230</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E81" t="n">
-        <v>24</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>46231</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E82" t="n">
-        <v>24</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>46232</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E83" t="n">
-        <v>24</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>46233</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E84" t="n">
-        <v>24</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E85" t="n">
-        <v>24</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
-        <v>46235</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E86" t="n">
-        <v>24</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
-        <v>46237</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E87" t="n">
-        <v>24</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
-        <v>46238</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E88" t="n">
-        <v>24</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
-        <v>46239</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E89" t="n">
-        <v>24</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
-        <v>46240</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E90" t="n">
-        <v>24</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
-        <v>46241</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E91" t="n">
-        <v>24</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
-        <v>46242</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E92" t="n">
-        <v>24</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
-        <v>46244</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E93" t="n">
-        <v>24</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>46245</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E94" t="n">
-        <v>24</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>46246</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E95" t="n">
-        <v>24</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
-        <v>46247</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E96" t="n">
-        <v>24</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="n">
-        <v>46248</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E97" t="n">
-        <v>24</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="n">
-        <v>46249</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E98" t="n">
-        <v>24</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="n">
-        <v>46251</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E99" t="n">
-        <v>24</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Z 1325 sece zawieszka mix luz</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>552.66</v>
-      </c>
-      <c r="E100" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>45758</v>
-      </c>
-      <c r="H100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>813.39</v>
-      </c>
-      <c r="E101" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="n">
-        <v>46253</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E102" t="n">
-        <v>24</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="n">
-        <v>46254</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E103" t="n">
-        <v>24</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E104" t="n">
-        <v>24</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="n">
-        <v>46256</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E105" t="n">
-        <v>24</v>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E106" t="n">
-        <v>24</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E107" t="n">
-        <v>24</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E108" t="n">
-        <v>24</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="n">
-        <v>46261</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E109" t="n">
-        <v>24</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E110" t="n">
-        <v>24</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="n">
-        <v>46263</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E111" t="n">
-        <v>24</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E112" t="n">
-        <v>24</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E113" t="n">
-        <v>24</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E114" t="n">
-        <v>24</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E115" t="n">
-        <v>24</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E116" t="n">
-        <v>24</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E117" t="n">
-        <v>24</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E118" t="n">
-        <v>24</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E119" t="n">
-        <v>24</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="n">
-        <v>46274</v>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E120" t="n">
-        <v>24</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E121" t="n">
-        <v>24</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E122" t="n">
-        <v>24</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>1320</v>
-      </c>
-      <c r="E123" t="n">
-        <v>24</v>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Waza Ceim kolor mix</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>818.61</v>
-      </c>
-      <c r="E124" t="n">
-        <v>14.88</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>364.65</v>
-      </c>
-      <c r="E125" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>960</v>
-      </c>
-      <c r="E126" t="n">
-        <v>24</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>960</v>
-      </c>
-      <c r="E127" t="n">
-        <v>24</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>960</v>
-      </c>
-      <c r="E128" t="n">
-        <v>24</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>960</v>
-      </c>
-      <c r="E129" t="n">
-        <v>24</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
-        <v>46284</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>960</v>
-      </c>
-      <c r="E130" t="n">
-        <v>24</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>960</v>
-      </c>
-      <c r="E131" t="n">
-        <v>24</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>960</v>
-      </c>
-      <c r="E132" t="n">
-        <v>24</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>960</v>
-      </c>
-      <c r="E133" t="n">
-        <v>24</v>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>960</v>
-      </c>
-      <c r="E134" t="n">
-        <v>24</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H134" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>960</v>
-      </c>
-      <c r="E135" t="n">
-        <v>24</v>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>960</v>
-      </c>
-      <c r="E136" t="n">
-        <v>24</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>960</v>
-      </c>
-      <c r="E137" t="n">
-        <v>24</v>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>960</v>
-      </c>
-      <c r="E138" t="n">
-        <v>24</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>960</v>
-      </c>
-      <c r="E139" t="n">
-        <v>24</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>960</v>
-      </c>
-      <c r="E140" t="n">
-        <v>24</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H140" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
-        <v>46297</v>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>960</v>
-      </c>
-      <c r="E141" t="n">
-        <v>24</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H141" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
-        <v>46298</v>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>960</v>
-      </c>
-      <c r="E142" t="n">
-        <v>24</v>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H142" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="n">
-        <v>46300</v>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>960</v>
-      </c>
-      <c r="E143" t="n">
-        <v>24</v>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H143" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="n">
-        <v>46301</v>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>960</v>
-      </c>
-      <c r="E144" t="n">
-        <v>24</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H144" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="n">
-        <v>46302</v>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>960</v>
-      </c>
-      <c r="E145" t="n">
-        <v>24</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="n">
-        <v>46303</v>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>960</v>
-      </c>
-      <c r="E146" t="n">
-        <v>24</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H146" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="n">
-        <v>46304</v>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>960</v>
-      </c>
-      <c r="E147" t="n">
-        <v>24</v>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H147" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="n">
-        <v>46305</v>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>960</v>
-      </c>
-      <c r="E148" t="n">
-        <v>24</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H148" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="n">
-        <v>46307</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>960</v>
-      </c>
-      <c r="E149" t="n">
-        <v>24</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H149" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>960</v>
-      </c>
-      <c r="E150" t="n">
-        <v>24</v>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>960</v>
-      </c>
-      <c r="E151" t="n">
-        <v>24</v>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>960</v>
-      </c>
-      <c r="E152" t="n">
-        <v>24</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H152" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>960</v>
-      </c>
-      <c r="E153" t="n">
-        <v>24</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H153" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>960</v>
-      </c>
-      <c r="E154" t="n">
-        <v>24</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H154" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>960</v>
-      </c>
-      <c r="E155" t="n">
-        <v>24</v>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H155" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="n">
-        <v>46315</v>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>960</v>
-      </c>
-      <c r="E156" t="n">
-        <v>24</v>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H156" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>960</v>
-      </c>
-      <c r="E157" t="n">
-        <v>24</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H157" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>960</v>
-      </c>
-      <c r="E158" t="n">
-        <v>24</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H158" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>960</v>
-      </c>
-      <c r="E159" t="n">
-        <v>24</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H159" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>960</v>
-      </c>
-      <c r="E160" t="n">
-        <v>24</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H160" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="n">
-        <v>46321</v>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>960</v>
-      </c>
-      <c r="E161" t="n">
-        <v>24</v>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G161" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H161" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>960</v>
-      </c>
-      <c r="E162" t="n">
-        <v>24</v>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G162" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>960</v>
-      </c>
-      <c r="E163" t="n">
-        <v>24</v>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="n">
-        <v>46324</v>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>960</v>
-      </c>
-      <c r="E164" t="n">
-        <v>24</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H164" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="n">
-        <v>46325</v>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>960</v>
-      </c>
-      <c r="E165" t="n">
-        <v>24</v>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="n">
-        <v>46326</v>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>960</v>
-      </c>
-      <c r="E166" t="n">
-        <v>24</v>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="n">
-        <v>46328</v>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>960</v>
-      </c>
-      <c r="E167" t="n">
-        <v>24</v>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H167" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="n">
-        <v>46329</v>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>960</v>
-      </c>
-      <c r="E168" t="n">
-        <v>24</v>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H168" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="n">
-        <v>46330</v>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>ZDK aplikacja M2 mix</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>547.35</v>
-      </c>
-      <c r="E169" t="n">
-        <v>13.68</v>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H169" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="n">
-        <v>46330</v>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>CZNI40276</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Serce 1325 solar mix</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>515.8099999999999</v>
-      </c>
-      <c r="E170" t="n">
-        <v>10.32</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G170" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H170" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="n">
-        <v>46331</v>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>CZNI40276</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Serce 1325 solar mix</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E171" t="n">
-        <v>24</v>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H171" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="n">
-        <v>46332</v>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>CZNI40276</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Serce 1325 solar mix</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E172" t="n">
-        <v>24</v>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G172" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H172" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="n">
-        <v>46333</v>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>CZNI40276</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Serce 1325 solar mix</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E173" t="n">
-        <v>24</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H173" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="n">
-        <v>46335</v>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>CZNI40276</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Serce 1325 solar mix</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>924.1900000000001</v>
-      </c>
-      <c r="E174" t="n">
-        <v>18.48</v>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G174" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="H174" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="n">
-        <v>46335</v>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>CZNI42027</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>P 109 serce SR</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>275.81</v>
-      </c>
-      <c r="E175" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="n">
-        <v>45820</v>
-      </c>
-      <c r="H175" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="n">
-        <v>46336</v>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>CZNI42027</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>P 109 serce SR</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E176" t="n">
-        <v>24</v>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G176" s="2" t="n">
-        <v>45820</v>
-      </c>
-      <c r="H176" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="n">
-        <v>46337</v>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>CZNI42027</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>P 109 serce SR</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E177" t="n">
-        <v>24</v>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G177" s="2" t="n">
-        <v>45820</v>
-      </c>
-      <c r="H177" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="n">
-        <v>46338</v>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>CZNI42027</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>P 109 serce SR</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>968.1900000000001</v>
-      </c>
-      <c r="E178" t="n">
-        <v>19.36</v>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G178" s="2" t="n">
-        <v>45820</v>
-      </c>
-      <c r="H178" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="n">
-        <v>46338</v>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>CZNI42034</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>P 109 serce ZŁ</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>231.81</v>
-      </c>
-      <c r="E179" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G179" s="2" t="n">
-        <v>45820</v>
-      </c>
-      <c r="H179" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="n">
-        <v>46339</v>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>CZNI42034</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>P 109 serce ZŁ</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E180" t="n">
-        <v>24</v>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G180" s="2" t="n">
-        <v>45820</v>
-      </c>
-      <c r="H180" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="n">
-        <v>46340</v>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>CZNI42034</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>P 109 serce ZŁ</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E181" t="n">
-        <v>24</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G181" s="2" t="n">
-        <v>45820</v>
-      </c>
-      <c r="H181" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27415,7 +22405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FM14"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27423,170 +22413,6 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="10" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
-    <col width="10" customWidth="1" min="30" max="30"/>
-    <col width="10" customWidth="1" min="31" max="31"/>
-    <col width="10" customWidth="1" min="32" max="32"/>
-    <col width="10" customWidth="1" min="33" max="33"/>
-    <col width="10" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
-    <col width="10" customWidth="1" min="36" max="36"/>
-    <col width="10" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
-    <col width="10" customWidth="1" min="39" max="39"/>
-    <col width="10" customWidth="1" min="40" max="40"/>
-    <col width="10" customWidth="1" min="41" max="41"/>
-    <col width="10" customWidth="1" min="42" max="42"/>
-    <col width="10" customWidth="1" min="43" max="43"/>
-    <col width="10" customWidth="1" min="44" max="44"/>
-    <col width="10" customWidth="1" min="45" max="45"/>
-    <col width="10" customWidth="1" min="46" max="46"/>
-    <col width="10" customWidth="1" min="47" max="47"/>
-    <col width="10" customWidth="1" min="48" max="48"/>
-    <col width="10" customWidth="1" min="49" max="49"/>
-    <col width="10" customWidth="1" min="50" max="50"/>
-    <col width="10" customWidth="1" min="51" max="51"/>
-    <col width="10" customWidth="1" min="52" max="52"/>
-    <col width="10" customWidth="1" min="53" max="53"/>
-    <col width="10" customWidth="1" min="54" max="54"/>
-    <col width="10" customWidth="1" min="55" max="55"/>
-    <col width="10" customWidth="1" min="56" max="56"/>
-    <col width="10" customWidth="1" min="57" max="57"/>
-    <col width="10" customWidth="1" min="58" max="58"/>
-    <col width="10" customWidth="1" min="59" max="59"/>
-    <col width="10" customWidth="1" min="60" max="60"/>
-    <col width="10" customWidth="1" min="61" max="61"/>
-    <col width="10" customWidth="1" min="62" max="62"/>
-    <col width="10" customWidth="1" min="63" max="63"/>
-    <col width="10" customWidth="1" min="64" max="64"/>
-    <col width="10" customWidth="1" min="65" max="65"/>
-    <col width="10" customWidth="1" min="66" max="66"/>
-    <col width="10" customWidth="1" min="67" max="67"/>
-    <col width="10" customWidth="1" min="68" max="68"/>
-    <col width="10" customWidth="1" min="69" max="69"/>
-    <col width="10" customWidth="1" min="70" max="70"/>
-    <col width="10" customWidth="1" min="71" max="71"/>
-    <col width="10" customWidth="1" min="72" max="72"/>
-    <col width="10" customWidth="1" min="73" max="73"/>
-    <col width="10" customWidth="1" min="74" max="74"/>
-    <col width="10" customWidth="1" min="75" max="75"/>
-    <col width="10" customWidth="1" min="76" max="76"/>
-    <col width="10" customWidth="1" min="77" max="77"/>
-    <col width="10" customWidth="1" min="78" max="78"/>
-    <col width="10" customWidth="1" min="79" max="79"/>
-    <col width="10" customWidth="1" min="80" max="80"/>
-    <col width="10" customWidth="1" min="81" max="81"/>
-    <col width="10" customWidth="1" min="82" max="82"/>
-    <col width="10" customWidth="1" min="83" max="83"/>
-    <col width="10" customWidth="1" min="84" max="84"/>
-    <col width="10" customWidth="1" min="85" max="85"/>
-    <col width="10" customWidth="1" min="86" max="86"/>
-    <col width="10" customWidth="1" min="87" max="87"/>
-    <col width="10" customWidth="1" min="88" max="88"/>
-    <col width="10" customWidth="1" min="89" max="89"/>
-    <col width="10" customWidth="1" min="90" max="90"/>
-    <col width="10" customWidth="1" min="91" max="91"/>
-    <col width="10" customWidth="1" min="92" max="92"/>
-    <col width="10" customWidth="1" min="93" max="93"/>
-    <col width="10" customWidth="1" min="94" max="94"/>
-    <col width="10" customWidth="1" min="95" max="95"/>
-    <col width="10" customWidth="1" min="96" max="96"/>
-    <col width="10" customWidth="1" min="97" max="97"/>
-    <col width="10" customWidth="1" min="98" max="98"/>
-    <col width="10" customWidth="1" min="99" max="99"/>
-    <col width="10" customWidth="1" min="100" max="100"/>
-    <col width="10" customWidth="1" min="101" max="101"/>
-    <col width="10" customWidth="1" min="102" max="102"/>
-    <col width="10" customWidth="1" min="103" max="103"/>
-    <col width="10" customWidth="1" min="104" max="104"/>
-    <col width="10" customWidth="1" min="105" max="105"/>
-    <col width="10" customWidth="1" min="106" max="106"/>
-    <col width="10" customWidth="1" min="107" max="107"/>
-    <col width="10" customWidth="1" min="108" max="108"/>
-    <col width="10" customWidth="1" min="109" max="109"/>
-    <col width="10" customWidth="1" min="110" max="110"/>
-    <col width="10" customWidth="1" min="111" max="111"/>
-    <col width="10" customWidth="1" min="112" max="112"/>
-    <col width="10" customWidth="1" min="113" max="113"/>
-    <col width="10" customWidth="1" min="114" max="114"/>
-    <col width="10" customWidth="1" min="115" max="115"/>
-    <col width="10" customWidth="1" min="116" max="116"/>
-    <col width="10" customWidth="1" min="117" max="117"/>
-    <col width="10" customWidth="1" min="118" max="118"/>
-    <col width="10" customWidth="1" min="119" max="119"/>
-    <col width="10" customWidth="1" min="120" max="120"/>
-    <col width="10" customWidth="1" min="121" max="121"/>
-    <col width="10" customWidth="1" min="122" max="122"/>
-    <col width="10" customWidth="1" min="123" max="123"/>
-    <col width="10" customWidth="1" min="124" max="124"/>
-    <col width="10" customWidth="1" min="125" max="125"/>
-    <col width="10" customWidth="1" min="126" max="126"/>
-    <col width="10" customWidth="1" min="127" max="127"/>
-    <col width="10" customWidth="1" min="128" max="128"/>
-    <col width="10" customWidth="1" min="129" max="129"/>
-    <col width="10" customWidth="1" min="130" max="130"/>
-    <col width="10" customWidth="1" min="131" max="131"/>
-    <col width="10" customWidth="1" min="132" max="132"/>
-    <col width="10" customWidth="1" min="133" max="133"/>
-    <col width="10" customWidth="1" min="134" max="134"/>
-    <col width="10" customWidth="1" min="135" max="135"/>
-    <col width="10" customWidth="1" min="136" max="136"/>
-    <col width="10" customWidth="1" min="137" max="137"/>
-    <col width="10" customWidth="1" min="138" max="138"/>
-    <col width="10" customWidth="1" min="139" max="139"/>
-    <col width="10" customWidth="1" min="140" max="140"/>
-    <col width="10" customWidth="1" min="141" max="141"/>
-    <col width="10" customWidth="1" min="142" max="142"/>
-    <col width="10" customWidth="1" min="143" max="143"/>
-    <col width="10" customWidth="1" min="144" max="144"/>
-    <col width="10" customWidth="1" min="145" max="145"/>
-    <col width="10" customWidth="1" min="146" max="146"/>
-    <col width="10" customWidth="1" min="147" max="147"/>
-    <col width="10" customWidth="1" min="148" max="148"/>
-    <col width="10" customWidth="1" min="149" max="149"/>
-    <col width="10" customWidth="1" min="150" max="150"/>
-    <col width="10" customWidth="1" min="151" max="151"/>
-    <col width="10" customWidth="1" min="152" max="152"/>
-    <col width="10" customWidth="1" min="153" max="153"/>
-    <col width="10" customWidth="1" min="154" max="154"/>
-    <col width="10" customWidth="1" min="155" max="155"/>
-    <col width="10" customWidth="1" min="156" max="156"/>
-    <col width="10" customWidth="1" min="157" max="157"/>
-    <col width="10" customWidth="1" min="158" max="158"/>
-    <col width="10" customWidth="1" min="159" max="159"/>
-    <col width="10" customWidth="1" min="160" max="160"/>
-    <col width="10" customWidth="1" min="161" max="161"/>
-    <col width="10" customWidth="1" min="162" max="162"/>
-    <col width="10" customWidth="1" min="163" max="163"/>
-    <col width="10" customWidth="1" min="164" max="164"/>
-    <col width="10" customWidth="1" min="165" max="165"/>
-    <col width="10" customWidth="1" min="166" max="166"/>
-    <col width="10" customWidth="1" min="167" max="167"/>
-    <col width="10" customWidth="1" min="168" max="168"/>
-    <col width="10" customWidth="1" min="169" max="169"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27607,1128 +22433,114 @@
       <c r="E1" s="2" t="n">
         <v>46148</v>
       </c>
-      <c r="F1" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="G1" s="2" t="n">
-        <v>46150</v>
-      </c>
-      <c r="H1" s="2" t="n">
-        <v>46151</v>
-      </c>
-      <c r="I1" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="J1" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="K1" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="L1" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="M1" s="2" t="n">
-        <v>46158</v>
-      </c>
-      <c r="N1" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="O1" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="P1" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="Q1" s="2" t="n">
-        <v>46163</v>
-      </c>
-      <c r="R1" s="2" t="n">
-        <v>46164</v>
-      </c>
-      <c r="S1" s="2" t="n">
-        <v>46165</v>
-      </c>
-      <c r="T1" s="2" t="n">
-        <v>46167</v>
-      </c>
-      <c r="U1" s="2" t="n">
-        <v>46168</v>
-      </c>
-      <c r="V1" s="2" t="n">
-        <v>46169</v>
-      </c>
-      <c r="W1" s="2" t="n">
-        <v>46170</v>
-      </c>
-      <c r="X1" s="2" t="n">
-        <v>46171</v>
-      </c>
-      <c r="Y1" s="2" t="n">
-        <v>46172</v>
-      </c>
-      <c r="Z1" s="2" t="n">
-        <v>46174</v>
-      </c>
-      <c r="AA1" s="2" t="n">
-        <v>46175</v>
-      </c>
-      <c r="AB1" s="2" t="n">
-        <v>46176</v>
-      </c>
-      <c r="AC1" s="2" t="n">
-        <v>46177</v>
-      </c>
-      <c r="AD1" s="2" t="n">
-        <v>46178</v>
-      </c>
-      <c r="AE1" s="2" t="n">
-        <v>46179</v>
-      </c>
-      <c r="AF1" s="2" t="n">
-        <v>46181</v>
-      </c>
-      <c r="AG1" s="2" t="n">
-        <v>46182</v>
-      </c>
-      <c r="AH1" s="2" t="n">
-        <v>46183</v>
-      </c>
-      <c r="AI1" s="2" t="n">
-        <v>46184</v>
-      </c>
-      <c r="AJ1" s="2" t="n">
-        <v>46185</v>
-      </c>
-      <c r="AK1" s="2" t="n">
-        <v>46186</v>
-      </c>
-      <c r="AL1" s="2" t="n">
-        <v>46188</v>
-      </c>
-      <c r="AM1" s="2" t="n">
-        <v>46189</v>
-      </c>
-      <c r="AN1" s="2" t="n">
-        <v>46190</v>
-      </c>
-      <c r="AO1" s="2" t="n">
-        <v>46191</v>
-      </c>
-      <c r="AP1" s="2" t="n">
-        <v>46192</v>
-      </c>
-      <c r="AQ1" s="2" t="n">
-        <v>46193</v>
-      </c>
-      <c r="AR1" s="2" t="n">
-        <v>46195</v>
-      </c>
-      <c r="AS1" s="2" t="n">
-        <v>46196</v>
-      </c>
-      <c r="AT1" s="2" t="n">
-        <v>46197</v>
-      </c>
-      <c r="AU1" s="2" t="n">
-        <v>46198</v>
-      </c>
-      <c r="AV1" s="2" t="n">
-        <v>46199</v>
-      </c>
-      <c r="AW1" s="2" t="n">
-        <v>46200</v>
-      </c>
-      <c r="AX1" s="2" t="n">
-        <v>46202</v>
-      </c>
-      <c r="AY1" s="2" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AZ1" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="BA1" s="2" t="n">
-        <v>46205</v>
-      </c>
-      <c r="BB1" s="2" t="n">
-        <v>46206</v>
-      </c>
-      <c r="BC1" s="2" t="n">
-        <v>46207</v>
-      </c>
-      <c r="BD1" s="2" t="n">
-        <v>46209</v>
-      </c>
-      <c r="BE1" s="2" t="n">
-        <v>46210</v>
-      </c>
-      <c r="BF1" s="2" t="n">
-        <v>46211</v>
-      </c>
-      <c r="BG1" s="2" t="n">
-        <v>46212</v>
-      </c>
-      <c r="BH1" s="2" t="n">
-        <v>46213</v>
-      </c>
-      <c r="BI1" s="2" t="n">
-        <v>46214</v>
-      </c>
-      <c r="BJ1" s="2" t="n">
-        <v>46216</v>
-      </c>
-      <c r="BK1" s="2" t="n">
-        <v>46217</v>
-      </c>
-      <c r="BL1" s="2" t="n">
-        <v>46218</v>
-      </c>
-      <c r="BM1" s="2" t="n">
-        <v>46219</v>
-      </c>
-      <c r="BN1" s="2" t="n">
-        <v>46220</v>
-      </c>
-      <c r="BO1" s="2" t="n">
-        <v>46221</v>
-      </c>
-      <c r="BP1" s="2" t="n">
-        <v>46223</v>
-      </c>
-      <c r="BQ1" s="2" t="n">
-        <v>46224</v>
-      </c>
-      <c r="BR1" s="2" t="n">
-        <v>46225</v>
-      </c>
-      <c r="BS1" s="2" t="n">
-        <v>46226</v>
-      </c>
-      <c r="BT1" s="2" t="n">
-        <v>46227</v>
-      </c>
-      <c r="BU1" s="2" t="n">
-        <v>46228</v>
-      </c>
-      <c r="BV1" s="2" t="n">
-        <v>46230</v>
-      </c>
-      <c r="BW1" s="2" t="n">
-        <v>46231</v>
-      </c>
-      <c r="BX1" s="2" t="n">
-        <v>46232</v>
-      </c>
-      <c r="BY1" s="2" t="n">
-        <v>46233</v>
-      </c>
-      <c r="BZ1" s="2" t="n">
-        <v>46234</v>
-      </c>
-      <c r="CA1" s="2" t="n">
-        <v>46235</v>
-      </c>
-      <c r="CB1" s="2" t="n">
-        <v>46237</v>
-      </c>
-      <c r="CC1" s="2" t="n">
-        <v>46238</v>
-      </c>
-      <c r="CD1" s="2" t="n">
-        <v>46239</v>
-      </c>
-      <c r="CE1" s="2" t="n">
-        <v>46240</v>
-      </c>
-      <c r="CF1" s="2" t="n">
-        <v>46241</v>
-      </c>
-      <c r="CG1" s="2" t="n">
-        <v>46242</v>
-      </c>
-      <c r="CH1" s="2" t="n">
-        <v>46244</v>
-      </c>
-      <c r="CI1" s="2" t="n">
-        <v>46245</v>
-      </c>
-      <c r="CJ1" s="2" t="n">
-        <v>46246</v>
-      </c>
-      <c r="CK1" s="2" t="n">
-        <v>46247</v>
-      </c>
-      <c r="CL1" s="2" t="n">
-        <v>46248</v>
-      </c>
-      <c r="CM1" s="2" t="n">
-        <v>46249</v>
-      </c>
-      <c r="CN1" s="2" t="n">
-        <v>46251</v>
-      </c>
-      <c r="CO1" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="CP1" s="2" t="n">
-        <v>46253</v>
-      </c>
-      <c r="CQ1" s="2" t="n">
-        <v>46254</v>
-      </c>
-      <c r="CR1" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="CS1" s="2" t="n">
-        <v>46256</v>
-      </c>
-      <c r="CT1" s="2" t="n">
-        <v>46258</v>
-      </c>
-      <c r="CU1" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="CV1" s="2" t="n">
-        <v>46260</v>
-      </c>
-      <c r="CW1" s="2" t="n">
-        <v>46261</v>
-      </c>
-      <c r="CX1" s="2" t="n">
-        <v>46262</v>
-      </c>
-      <c r="CY1" s="2" t="n">
-        <v>46263</v>
-      </c>
-      <c r="CZ1" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="DA1" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="DB1" s="2" t="n">
-        <v>46267</v>
-      </c>
-      <c r="DC1" s="2" t="n">
-        <v>46268</v>
-      </c>
-      <c r="DD1" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="DE1" s="2" t="n">
-        <v>46270</v>
-      </c>
-      <c r="DF1" s="2" t="n">
-        <v>46272</v>
-      </c>
-      <c r="DG1" s="2" t="n">
-        <v>46273</v>
-      </c>
-      <c r="DH1" s="2" t="n">
-        <v>46274</v>
-      </c>
-      <c r="DI1" s="2" t="n">
-        <v>46275</v>
-      </c>
-      <c r="DJ1" s="2" t="n">
-        <v>46276</v>
-      </c>
-      <c r="DK1" s="2" t="n">
-        <v>46277</v>
-      </c>
-      <c r="DL1" s="2" t="n">
-        <v>46279</v>
-      </c>
-      <c r="DM1" s="2" t="n">
-        <v>46280</v>
-      </c>
-      <c r="DN1" s="2" t="n">
-        <v>46281</v>
-      </c>
-      <c r="DO1" s="2" t="n">
-        <v>46282</v>
-      </c>
-      <c r="DP1" s="2" t="n">
-        <v>46283</v>
-      </c>
-      <c r="DQ1" s="2" t="n">
-        <v>46284</v>
-      </c>
-      <c r="DR1" s="2" t="n">
-        <v>46286</v>
-      </c>
-      <c r="DS1" s="2" t="n">
-        <v>46287</v>
-      </c>
-      <c r="DT1" s="2" t="n">
-        <v>46288</v>
-      </c>
-      <c r="DU1" s="2" t="n">
-        <v>46289</v>
-      </c>
-      <c r="DV1" s="2" t="n">
-        <v>46290</v>
-      </c>
-      <c r="DW1" s="2" t="n">
-        <v>46291</v>
-      </c>
-      <c r="DX1" s="2" t="n">
-        <v>46293</v>
-      </c>
-      <c r="DY1" s="2" t="n">
-        <v>46294</v>
-      </c>
-      <c r="DZ1" s="2" t="n">
-        <v>46295</v>
-      </c>
-      <c r="EA1" s="2" t="n">
-        <v>46296</v>
-      </c>
-      <c r="EB1" s="2" t="n">
-        <v>46297</v>
-      </c>
-      <c r="EC1" s="2" t="n">
-        <v>46298</v>
-      </c>
-      <c r="ED1" s="2" t="n">
-        <v>46300</v>
-      </c>
-      <c r="EE1" s="2" t="n">
-        <v>46301</v>
-      </c>
-      <c r="EF1" s="2" t="n">
-        <v>46302</v>
-      </c>
-      <c r="EG1" s="2" t="n">
-        <v>46303</v>
-      </c>
-      <c r="EH1" s="2" t="n">
-        <v>46304</v>
-      </c>
-      <c r="EI1" s="2" t="n">
-        <v>46305</v>
-      </c>
-      <c r="EJ1" s="2" t="n">
-        <v>46307</v>
-      </c>
-      <c r="EK1" s="2" t="n">
-        <v>46308</v>
-      </c>
-      <c r="EL1" s="2" t="n">
-        <v>46309</v>
-      </c>
-      <c r="EM1" s="2" t="n">
-        <v>46310</v>
-      </c>
-      <c r="EN1" s="2" t="n">
-        <v>46311</v>
-      </c>
-      <c r="EO1" s="2" t="n">
-        <v>46312</v>
-      </c>
-      <c r="EP1" s="2" t="n">
-        <v>46314</v>
-      </c>
-      <c r="EQ1" s="2" t="n">
-        <v>46315</v>
-      </c>
-      <c r="ER1" s="2" t="n">
-        <v>46316</v>
-      </c>
-      <c r="ES1" s="2" t="n">
-        <v>46317</v>
-      </c>
-      <c r="ET1" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="EU1" s="2" t="n">
-        <v>46319</v>
-      </c>
-      <c r="EV1" s="2" t="n">
-        <v>46321</v>
-      </c>
-      <c r="EW1" s="2" t="n">
-        <v>46322</v>
-      </c>
-      <c r="EX1" s="2" t="n">
-        <v>46323</v>
-      </c>
-      <c r="EY1" s="2" t="n">
-        <v>46324</v>
-      </c>
-      <c r="EZ1" s="2" t="n">
-        <v>46325</v>
-      </c>
-      <c r="FA1" s="2" t="n">
-        <v>46326</v>
-      </c>
-      <c r="FB1" s="2" t="n">
-        <v>46328</v>
-      </c>
-      <c r="FC1" s="2" t="n">
-        <v>46329</v>
-      </c>
-      <c r="FD1" s="2" t="n">
-        <v>46330</v>
-      </c>
-      <c r="FE1" s="2" t="n">
-        <v>46331</v>
-      </c>
-      <c r="FF1" s="2" t="n">
-        <v>46332</v>
-      </c>
-      <c r="FG1" s="2" t="n">
-        <v>46333</v>
-      </c>
-      <c r="FH1" s="2" t="n">
-        <v>46335</v>
-      </c>
-      <c r="FI1" s="2" t="n">
-        <v>46336</v>
-      </c>
-      <c r="FJ1" s="2" t="n">
-        <v>46337</v>
-      </c>
-      <c r="FK1" s="2" t="n">
-        <v>46338</v>
-      </c>
-      <c r="FL1" s="2" t="n">
-        <v>46339</v>
-      </c>
-      <c r="FM1" s="2" t="n">
-        <v>46340</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CZNI38914</t>
-        </is>
-      </c>
-      <c r="CO2" s="4" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="CP2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CQ2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CR2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CS2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CT2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CU2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CV2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CW2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CX2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CY2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CZ2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DA2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DB2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DC2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DD2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DE2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DF2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DG2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DH2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DI2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DJ2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DK2" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DL2" s="4" t="n">
-        <v>14.88</v>
+          <t>CZNI14475</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>6.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CZNI39096</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>1.46</v>
+          <t>CZNI19456</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CZNI39508</t>
-        </is>
-      </c>
-      <c r="AW4" s="4" t="n">
-        <v>14.65</v>
-      </c>
-      <c r="AX4" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AY4" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ4" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA4" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB4" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC4" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD4" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE4" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BF4" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BG4" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BH4" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BI4" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BJ4" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BK4" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BL4" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BM4" s="4" t="n">
-        <v>4.99</v>
+          <t>CZNI25610</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CZNI39522</t>
-        </is>
-      </c>
-      <c r="DL5" s="4" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="DM5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DN5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DO5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DP5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DQ5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DR5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DS5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DT5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DU5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DV5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DW5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DX5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DY5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="DZ5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EA5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EB5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EC5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="ED5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EE5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EF5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EG5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EH5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EI5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EJ5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EK5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EL5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EM5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EN5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EO5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EP5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EQ5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="ER5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="ES5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="ET5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EU5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EV5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EW5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EX5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EY5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="EZ5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="FA5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="FB5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="FC5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="FD5" s="4" t="n">
-        <v>13.68</v>
+          <t>CZNI27058</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CZNI39539</t>
-        </is>
-      </c>
-      <c r="AJ6" s="4" t="n">
-        <v>7.08</v>
-      </c>
-      <c r="AK6" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL6" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM6" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AN6" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO6" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP6" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AQ6" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR6" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS6" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT6" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AU6" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AV6" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW6" s="4" t="n">
-        <v>9.35</v>
+          <t>CZNI27461</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CZNI39690</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>40</v>
+          <t>CZNI27478</t>
+        </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>66.09999999999999</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CZNI39805L</t>
-        </is>
-      </c>
-      <c r="BM8" s="4" t="n">
-        <v>19.01</v>
-      </c>
-      <c r="BN8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BO8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BP8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BQ8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BR8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BS8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BT8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BU8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BV8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BW8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BX8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BY8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BZ8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CA8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CB8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CC8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CD8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CE8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CF8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CG8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CH8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CI8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CJ8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CK8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CL8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CM8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CN8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="CO8" s="4" t="n">
-        <v>9.210000000000001</v>
+          <t>CZNI28000</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CZNI39843</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>22.54</v>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="W9" s="4" t="n">
-        <v>11.42</v>
+          <t>CZNI28376</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>1.54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CZNI40115</t>
-        </is>
-      </c>
-      <c r="AB10" s="4" t="n">
-        <v>10.28</v>
-      </c>
-      <c r="AC10" s="4" t="n">
+          <t>CZNI42843</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="AD10" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE10" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF10" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG10" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH10" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI10" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AJ10" s="4" t="n">
-        <v>16.92</v>
+      <c r="C10" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CZNI40276</t>
-        </is>
-      </c>
-      <c r="FD11" s="4" t="n">
-        <v>10.32</v>
-      </c>
-      <c r="FE11" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="FF11" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="FG11" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="FH11" s="4" t="n">
-        <v>18.48</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CZNI40283</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="n">
-        <v>12.58</v>
-      </c>
-      <c r="X12" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y12" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z12" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA12" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB12" s="4" t="n">
-        <v>13.72</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CZNI42027</t>
-        </is>
-      </c>
-      <c r="FH13" s="4" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="FI13" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="FJ13" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="FK13" s="4" t="n">
-        <v>19.36</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CZNI42034</t>
-        </is>
-      </c>
-      <c r="FK14" s="4" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="FL14" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="FM14" s="4" t="n">
-        <v>24</v>
+          <t>CZNI42850</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>
